--- a/data/trans_camb/IP16A04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Habitat-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 16,62</t>
+          <t>1,82; 15,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,16</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,26</t>
+          <t>1,05; 9,93</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 0,0</t>
+          <t>-8,12; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 5,31</t>
+          <t>-4,78; 5,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 2,43</t>
+          <t>-5,51; 2,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,92</t>
+          <t>-5,1; 2,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,93</t>
+          <t>-4,34; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 3,05</t>
+          <t>-3,38; 3,13</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,56</t>
+          <t>0,0; 7,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 2,38</t>
+          <t>-6,71; 2,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 0,0</t>
+          <t>-9,91; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,17</t>
+          <t>-3,34; 2,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 0,0</t>
+          <t>-5,63; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 0,0</t>
+          <t>-15,15; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 3,58</t>
+          <t>-11,8; 3,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 2,58</t>
+          <t>-8,34; 2,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 0,0</t>
+          <t>-12,52; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 0,63</t>
+          <t>-8,09; 0,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 0,97</t>
+          <t>-6,96; 0,98</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,34</t>
+          <t>-3,53; 0,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,95</t>
+          <t>-1,14; 3,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,01</t>
+          <t>-3,05; 1,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,39</t>
+          <t>-3,08; 1,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,45</t>
+          <t>-2,26; 0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,98</t>
+          <t>-1,26; 1,98</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,66; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-91,97; 170,12</t>
+          <t>-92,22; 206,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 438,74</t>
+          <t>-66,48; 384,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Habitat-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,35</t>
+          <t>1,85; 16,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,49</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,93</t>
+          <t>1,06; 10,04</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,0</t>
+          <t>-8,02; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,14</t>
+          <t>-4,4; 5,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 2,45</t>
+          <t>-6,36; 2,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,93</t>
+          <t>-5,14; 2,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,62</t>
+          <t>-5,04; 0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,13</t>
+          <t>-3,34; 3,32</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,69</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 2,35</t>
+          <t>-7,6; 2,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 0,0</t>
+          <t>-10,8; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,63</t>
+          <t>-3,17; 2,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 0,0</t>
+          <t>-5,64; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 0,0</t>
+          <t>-14,98; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 3,59</t>
+          <t>-12,29; 3,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 2,57</t>
+          <t>-8,27; 2,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 0,0</t>
+          <t>-11,08; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 0,64</t>
+          <t>-7,34; 0,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,98</t>
+          <t>-6,52; 1,66</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,34</t>
+          <t>-3,26; 0,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,85</t>
+          <t>-1,16; 4,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,15</t>
+          <t>-2,95; 1,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,34</t>
+          <t>-3,08; 1,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,41</t>
+          <t>-2,25; 0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,98</t>
+          <t>-1,36; 2,12</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,66; —</t>
+          <t>-72,99; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-92,22; 206,83</t>
+          <t>-91,48; 139,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 384,29</t>
+          <t>-66,56; 419,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Habitat-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumieron medicamentos laxantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2,27</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 16,64</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>1,87; 16,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,04</t>
+          <t>1,07; 10,26</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,25</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-1,61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 0,0</t>
+          <t>-6,51; 2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 5,56</t>
+          <t>-5,11; 2,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 2,47</t>
+          <t>-8,0; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,93</t>
+          <t>-3,6; 5,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 0,85</t>
+          <t>-4,31; 0,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,32</t>
+          <t>-2,93; 3,05</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-27,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-14,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>52,16%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-27,44%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-14,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,92</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>1,44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>-6,36; 2,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,82; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,37</t>
+          <t>0,0; 8,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,59</t>
+          <t>-3,71; 2,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,0</t>
+          <t>-5,33; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-38,17%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-38,17%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,09</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-2,99</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-1,2</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,09</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 0,0</t>
+          <t>-8,29; 2,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 3,55</t>
+          <t>-10,52; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 2,6</t>
+          <t>-15,54; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 0,0</t>
+          <t>-11,7; 3,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,64</t>
+          <t>-7,33; 0,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 1,66</t>
+          <t>-7,25; 0,97</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-38,71%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-40,04%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-38,71%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,81</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,33</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,34</t>
+          <t>-3,29; 1,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,04</t>
+          <t>-3,08; 1,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,17</t>
+          <t>-3,47; 0,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,32</t>
+          <t>-1,12; 3,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,41</t>
+          <t>-2,36; 0,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,12</t>
+          <t>-1,29; 1,98</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-35,54%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-39,07%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-70,73%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>116,23%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-35,54%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-39,07%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,99; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-91,48; 139,35</t>
+          <t>-91,97; 170,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,56; 419,99</t>
+          <t>-66,95; 438,74</t>
         </is>
       </c>
     </row>
